--- a/TOP_Code_Lookup.xlsx
+++ b/TOP_Code_Lookup.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TOP Code Lookup" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CCC Discipline Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="TOP Code Lookup" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="CCC Discipline Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TOP Code Lookup'!$A$1:$F$199</definedName>
@@ -1030,7 +1030,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0612</t>
+          <t>0614</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
@@ -1100,7 +1100,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0612</t>
+          <t>0614</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>0706</t>
+          <t>0708</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0708</t>
+          <t>0706</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>1118</t>
+          <t>0850</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1118</t>
+          <t>0850</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>0909</t>
+          <t>0953</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>0960</t>
+          <t>0708</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>0956</t>
+          <t>0952</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>0930</t>
+          <t>0936</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
@@ -1975,7 +1975,7 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>0958</t>
+          <t>0952</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -2010,7 +2010,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>0957</t>
+          <t>0946</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
@@ -2045,7 +2045,7 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>0953</t>
+          <t>0957</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>0946</t>
+          <t>0952</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
@@ -2185,7 +2185,7 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0956</t>
+          <t>0952</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -2220,7 +2220,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>0909</t>
+          <t>0953</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
@@ -2255,7 +2255,7 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0909</t>
+          <t>0953</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>0941</t>
+          <t>0956</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
@@ -2395,7 +2395,7 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0946</t>
+          <t>0952</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -2675,7 +2675,7 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>1010</t>
+          <t>1011</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>1014</t>
+          <t>1030</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
@@ -2780,7 +2780,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>1030</t>
+          <t>1009</t>
         </is>
       </c>
       <c r="E66" s="3" t="inlineStr">
@@ -2885,7 +2885,7 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>1106</t>
+          <t>1105</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>1108</t>
+          <t>1107</t>
         </is>
       </c>
       <c r="E70" s="3" t="inlineStr">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>1110</t>
+          <t>1108</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
@@ -3025,7 +3025,7 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>1120</t>
+          <t>1119</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
@@ -3060,7 +3060,7 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>1203</t>
+          <t>1201</t>
         </is>
       </c>
       <c r="E74" s="3" t="inlineStr">
@@ -3165,7 +3165,7 @@
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>1221</t>
         </is>
       </c>
       <c r="E77" s="5" t="inlineStr">
@@ -3200,7 +3200,7 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>1220</t>
+          <t>1230</t>
         </is>
       </c>
       <c r="E78" s="3" t="inlineStr">
@@ -3235,7 +3235,7 @@
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>1211</t>
+          <t>1230</t>
         </is>
       </c>
       <c r="E79" s="5" t="inlineStr">
@@ -3270,7 +3270,7 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>1222</t>
+          <t>1230</t>
         </is>
       </c>
       <c r="E80" s="3" t="inlineStr">
@@ -3305,7 +3305,7 @@
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>1201</t>
+          <t>1240</t>
         </is>
       </c>
       <c r="E81" s="5" t="inlineStr">
@@ -3340,7 +3340,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>1250</t>
+          <t>1240</t>
         </is>
       </c>
       <c r="E82" s="3" t="inlineStr">
@@ -3375,7 +3375,7 @@
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>1251</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
@@ -3410,7 +3410,7 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>1240</t>
+          <t>1250</t>
         </is>
       </c>
       <c r="E84" s="3" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>1304</t>
+          <t>1305</t>
         </is>
       </c>
       <c r="E86" s="3" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>1305</t>
+          <t>1306</t>
         </is>
       </c>
       <c r="E87" s="5" t="inlineStr">
@@ -3550,7 +3550,7 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>1305</t>
+          <t>1306</t>
         </is>
       </c>
       <c r="E88" s="3" t="inlineStr">
@@ -3690,7 +3690,7 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>1507</t>
+          <t>1520</t>
         </is>
       </c>
       <c r="E92" s="3" t="inlineStr">
@@ -3795,7 +3795,7 @@
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>1910</t>
+          <t>1914</t>
         </is>
       </c>
       <c r="E95" s="5" t="inlineStr">
@@ -3970,7 +3970,7 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>2130</t>
+          <t>2133</t>
         </is>
       </c>
       <c r="E100" s="3" t="inlineStr">
@@ -4005,7 +4005,7 @@
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>2130</t>
+          <t>2133</t>
         </is>
       </c>
       <c r="E101" s="5" t="inlineStr">
@@ -4040,7 +4040,7 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>2130</t>
+          <t>2133</t>
         </is>
       </c>
       <c r="E102" s="3" t="inlineStr">
@@ -4075,7 +4075,7 @@
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>2201</t>
+          <t>2202</t>
         </is>
       </c>
       <c r="E103" s="5" t="inlineStr">
@@ -4110,7 +4110,7 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>2203</t>
+          <t>2205</t>
         </is>
       </c>
       <c r="E104" s="3" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>2204</t>
+          <t>2206</t>
         </is>
       </c>
       <c r="E105" s="5" t="inlineStr">
@@ -4180,7 +4180,7 @@
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>2204</t>
+          <t>2206</t>
         </is>
       </c>
       <c r="E106" s="3" t="inlineStr">
@@ -4215,7 +4215,7 @@
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>2206</t>
+          <t>2208</t>
         </is>
       </c>
       <c r="E107" s="5" t="inlineStr">
@@ -4250,7 +4250,7 @@
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>2401</t>
+          <t>3007</t>
         </is>
       </c>
       <c r="E108" s="3" t="inlineStr">
@@ -4390,7 +4390,7 @@
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>4935</t>
+          <t>4932</t>
         </is>
       </c>
       <c r="E112" s="3" t="inlineStr">
@@ -4495,7 +4495,7 @@
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>0106</t>
+          <t>0112</t>
         </is>
       </c>
       <c r="E115" s="5" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>0100</t>
+          <t>0101</t>
         </is>
       </c>
       <c r="E116" s="3" t="inlineStr">
@@ -4775,7 +4775,7 @@
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>1130</t>
+          <t>1117</t>
         </is>
       </c>
       <c r="E123" s="5" t="inlineStr">
@@ -4985,7 +4985,7 @@
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>0946</t>
+          <t>0952</t>
         </is>
       </c>
       <c r="E129" s="5" t="inlineStr">
@@ -5090,7 +5090,7 @@
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="E132" s="3" t="inlineStr">
@@ -5125,7 +5125,7 @@
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>0952</t>
+          <t>0957</t>
         </is>
       </c>
       <c r="E133" s="5" t="inlineStr">
@@ -5335,7 +5335,7 @@
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>0946</t>
+          <t>0952</t>
         </is>
       </c>
       <c r="E139" s="5" t="inlineStr">
@@ -5405,7 +5405,7 @@
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>2202</t>
+          <t>2204</t>
         </is>
       </c>
       <c r="E141" s="5" t="inlineStr">
@@ -5580,7 +5580,7 @@
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>2130</t>
+          <t>2133</t>
         </is>
       </c>
       <c r="E146" s="3" t="inlineStr">
@@ -5615,7 +5615,7 @@
       </c>
       <c r="D147" s="4" t="inlineStr">
         <is>
-          <t>2207</t>
+          <t>2203</t>
         </is>
       </c>
       <c r="E147" s="5" t="inlineStr">
@@ -5720,7 +5720,7 @@
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>0606</t>
+          <t>0612</t>
         </is>
       </c>
       <c r="E150" s="3" t="inlineStr">
@@ -5895,7 +5895,7 @@
       </c>
       <c r="D155" s="4" t="inlineStr">
         <is>
-          <t>1112</t>
+          <t>1103</t>
         </is>
       </c>
       <c r="E155" s="5" t="inlineStr">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>1203</t>
+          <t>1201</t>
         </is>
       </c>
       <c r="E156" s="3" t="inlineStr">
@@ -6000,7 +6000,7 @@
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>1132</t>
+          <t>1111</t>
         </is>
       </c>
       <c r="E158" s="3" t="inlineStr">
@@ -6070,7 +6070,7 @@
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>1305</t>
+          <t>1306</t>
         </is>
       </c>
       <c r="E160" s="3" t="inlineStr">
@@ -6140,7 +6140,7 @@
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>1304</t>
+          <t>1305</t>
         </is>
       </c>
       <c r="E162" s="3" t="inlineStr">
@@ -6175,7 +6175,7 @@
       </c>
       <c r="D163" s="4" t="inlineStr">
         <is>
-          <t>0202</t>
+          <t>1302</t>
         </is>
       </c>
       <c r="E163" s="5" t="inlineStr">
@@ -6245,7 +6245,7 @@
       </c>
       <c r="D165" s="4" t="inlineStr">
         <is>
-          <t>1124</t>
+          <t>1117</t>
         </is>
       </c>
       <c r="E165" s="5" t="inlineStr">
@@ -6385,7 +6385,7 @@
       </c>
       <c r="D169" s="4" t="inlineStr">
         <is>
-          <t>0946</t>
+          <t>0952</t>
         </is>
       </c>
       <c r="E169" s="5" t="inlineStr">
@@ -6420,7 +6420,7 @@
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>0946</t>
+          <t>0952</t>
         </is>
       </c>
       <c r="E170" s="3" t="inlineStr">
@@ -6560,7 +6560,7 @@
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>2405</t>
+          <t>1255</t>
         </is>
       </c>
       <c r="E174" s="3" t="inlineStr">
@@ -6630,7 +6630,7 @@
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>1305</t>
+          <t>1306</t>
         </is>
       </c>
       <c r="E176" s="3" t="inlineStr">
@@ -6665,7 +6665,7 @@
       </c>
       <c r="D177" s="4" t="inlineStr">
         <is>
-          <t>1290</t>
+          <t>1222</t>
         </is>
       </c>
       <c r="E177" s="5" t="inlineStr">
@@ -6700,7 +6700,7 @@
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>1134</t>
+          <t>1199</t>
         </is>
       </c>
       <c r="E178" s="3" t="inlineStr">
@@ -6980,7 +6980,7 @@
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>2205</t>
+          <t>2207</t>
         </is>
       </c>
       <c r="E186" s="3" t="inlineStr">
@@ -7015,7 +7015,7 @@
       </c>
       <c r="D187" s="4" t="inlineStr">
         <is>
-          <t>1304</t>
+          <t>1305</t>
         </is>
       </c>
       <c r="E187" s="5" t="inlineStr">
@@ -7085,7 +7085,7 @@
       </c>
       <c r="D189" s="4" t="inlineStr">
         <is>
-          <t>0946</t>
+          <t>0952</t>
         </is>
       </c>
       <c r="E189" s="5" t="inlineStr">
@@ -7120,7 +7120,7 @@
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>0946</t>
+          <t>0952</t>
         </is>
       </c>
       <c r="E190" s="3" t="inlineStr">
@@ -7225,7 +7225,7 @@
       </c>
       <c r="D193" s="4" t="inlineStr">
         <is>
-          <t>2401</t>
+          <t>3009</t>
         </is>
       </c>
       <c r="E193" s="5" t="inlineStr">
@@ -7330,7 +7330,7 @@
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>1128</t>
+          <t>1117</t>
         </is>
       </c>
       <c r="E196" s="3" t="inlineStr">
@@ -7365,7 +7365,7 @@
       </c>
       <c r="D197" s="4" t="inlineStr">
         <is>
-          <t>0103</t>
+          <t>0104</t>
         </is>
       </c>
       <c r="E197" s="5" t="inlineStr">
